--- a/docs/实习计划.xlsx
+++ b/docs/实习计划.xlsx
@@ -1,31 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人\GitHub\CPI-Prediction\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F75B8BB-FD49-44BB-AFFD-330BEA78A440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242685EE-D60D-4DA1-BE57-8024D8565CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一周" sheetId="1" r:id="rId1"/>
+    <sheet name="第二周" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>模块</t>
   </si>
@@ -54,21 +50,6 @@
     <t>确定数据来源；下载/整理 CPI 月度数据；尽量补充相关经济指标，如 PPI、M2、利率、汇率、PMI、油价等；记录数据来源、时间范围、单位和频率</t>
   </si>
   <si>
-    <r>
-      <t>data_raw/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 原始数据文件；数据来源说明表</t>
-    </r>
-  </si>
-  <si>
     <t>数据清洗</t>
   </si>
   <si>
@@ -78,98 +59,19 @@
     <t>统一日期格式；统一月度频率；处理缺失值、重复值、异常值；确认 CPI 类型是指数、同比还是环比；按时间排序；画原始序列检查图</t>
   </si>
   <si>
-    <r>
-      <t>data_processed/cpi_monthly.csv</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>results/figures/cpi_series.png</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>；数据清洗说明</t>
-    </r>
-  </si>
-  <si>
     <t>样本构造</t>
   </si>
   <si>
+    <t>2人</t>
+  </si>
+  <si>
     <t>把时间序列转成监督学习样本</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">用过去 12 个月预测未来 1 个月；构造 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>X, y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>；按时间划分训练集和测试集；避免随机打乱；只用训练集拟合标准化器</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>src/data_utils.py</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>；训练/测试集构造说明</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>src/baselines.py</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>；各模型预测结果</t>
-    </r>
+    <t>对比评估</t>
+  </si>
+  <si>
+    <t>跑通第一版传统模型 baseline</t>
   </si>
   <si>
     <t>汇报整理</t>
@@ -184,80 +86,578 @@
     <t>汇总数据来源、清洗流程、样本构造方式、baseline 模型和初步结果；说明后续将加入 ESN 和光储备池</t>
   </si>
   <si>
-    <t>2人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>周五汇报、周日提交实习日记</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">实现 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+  </si>
+  <si>
+    <t>第二周目标</t>
+  </si>
+  <si>
+    <t>架构与仿真接口</t>
+  </si>
+  <si>
+    <t>杜艾佳（项目负责人）</t>
+  </si>
+  <si>
+    <t>跑通 CPI 到光储备池状态的完整接口，并确定孪生双支路总体结构</t>
+  </si>
+  <si>
+    <t>保留老师原始 ESN 文件不覆盖；复制并改造 CPI 专用脚本；确定 12 个月窗口、固定 mask、50 个虚拟节点和输入缩放方式；去除 NARMA 样本数与响应区间的硬编码；统一训练、验证、测试输入和状态提取接口；负责三部分最终联调与问题定位</t>
+  </si>
+  <si>
+    <t>CPI 光储备池输入脚本；动态状态提取脚本；孪生结构接口说明；联调记录</t>
+  </si>
+  <si>
+    <t>数据补充与核验</t>
+  </si>
+  <si>
+    <t>郑雪晴</t>
+  </si>
+  <si>
+    <t>完成双储备池状态比较、相似度读出和统一评估代码框架。</t>
+  </si>
+  <si>
+    <t>读取并缓存两个分支的储备池状态；实现状态绝对差、欧氏距离和相似度计算；先使用 Ridge/Logistic 完成简单孪生读出；预留共享线性读出接口；连接 CPI 回归预测头；统一计算 MAE、RMSE；整理普通光储备池、状态差孪生版本和对比学习版本的结果表及预测图。</t>
+  </si>
+  <si>
+    <t>储备池状态缓存文件；孪生读出代码；统一评估脚本；模型结果表；预测图与运行说明。</t>
+  </si>
+  <si>
+    <t>孪生回归样本对构造</t>
+  </si>
+  <si>
+    <t>陈中远</t>
+  </si>
+  <si>
+    <t>形成可供孪生光储备池回归使用的 CPI 样本对，并保证训练、验证、测试之间不存在时间泄漏</t>
+  </si>
+  <si>
+    <t>保留原有相似性判断规则，但仅用于样本配对和参考时期筛选，不再把 0/1 作为最终训练目标；在各自数据划分内部构造目标时期 i 与参考时期 j 的 12 个月窗口对；为每对样本计算连续回归标签 delta_cpi=CPI_i-CPI_j，并同时保存 CPI_i、CPI_j、样本索引、目标日期和可选相似标签；统计较小、中等、较大 CPI 差值区间的样本数量，避免样本对集中在单一区间；明确预测时参考时期 CPI_j 必须已知，且不得跨越时间边界使用未来信息</t>
+  </si>
+  <si>
+    <t>pair_indices_train.csv、pair_indices_val.csv、pair_indices_test.csv；样本对字段与相似性筛选规则说明；delta_cpi 分布统计；时间泄漏检查结果</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="等线"/>
         <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Naive、Linear Regression、SVR、Random Forest</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      </rPr>
+      <t>data_raw/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原始数据文件；数据来源说明表</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>；统一训练、预测流程；计算MAE、RMSE、MAPE；如果 CPI 有负值或接近 0，则 MAPE 改为 sMAPE 或只作为参考</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跑通第一版传统模型 baseline</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对比评估</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">实现 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Naive</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linear Regression</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SVR</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Random Forest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；统一训练、预测流程；计算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MAE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RMSE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MAPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；如果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CPI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有负值或接近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MAPE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>改为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sMAPE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或只作为参考</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+      </rPr>
+      <t>src/baselines.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；各模型预测结果</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>data_processed/cpi_monthly.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>results/figures/cpi_series.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；数据清洗说明</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">用过去 12 个月预测未来 1 个月；构造 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>X, y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；按时间划分训练集和测试集；避免随机打乱；只用训练集拟合标准化器</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+      </rPr>
+      <t>src/data_utils.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；训练</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试集构造说明</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+    </font>
+    <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
@@ -283,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -292,6 +692,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -357,74 +772,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -436,23 +791,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -462,23 +817,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -486,26 +841,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -540,17 +892,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -567,11 +919,6 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -601,11 +948,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="69.400000000000006">
+    <row r="2" spans="1:5" ht="74.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -614,72 +961,72 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
+      <c r="E2" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="118.15">
       <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="73.900000000000006">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>13</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="68.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="5" spans="1:5" ht="75.75">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="69.400000000000006">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
+      <c r="D5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="55.5">
       <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -687,7 +1034,93 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="14.73046875" customWidth="1"/>
+    <col min="2" max="2" width="16.46484375" customWidth="1"/>
+    <col min="3" max="3" width="23.73046875" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="28.1328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="55.5">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="83.25">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="55.5">
+      <c r="A4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/实习计划.xlsx
+++ b/docs/实习计划.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人\GitHub\CPI-Prediction\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242685EE-D60D-4DA1-BE57-8024D8565CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82200FE-D6EF-421A-8F81-C92E20784C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一周" sheetId="1" r:id="rId1"/>
@@ -107,19 +107,7 @@
     <t>CPI 光储备池输入脚本；动态状态提取脚本；孪生结构接口说明；联调记录</t>
   </si>
   <si>
-    <t>数据补充与核验</t>
-  </si>
-  <si>
     <t>郑雪晴</t>
-  </si>
-  <si>
-    <t>完成双储备池状态比较、相似度读出和统一评估代码框架。</t>
-  </si>
-  <si>
-    <t>读取并缓存两个分支的储备池状态；实现状态绝对差、欧氏距离和相似度计算；先使用 Ridge/Logistic 完成简单孪生读出；预留共享线性读出接口；连接 CPI 回归预测头；统一计算 MAE、RMSE；整理普通光储备池、状态差孪生版本和对比学习版本的结果表及预测图。</t>
-  </si>
-  <si>
-    <t>储备池状态缓存文件；孪生读出代码；统一评估脚本；模型结果表；预测图与运行说明。</t>
   </si>
   <si>
     <t>孪生回归样本对构造</t>
@@ -535,6 +523,22 @@
       </rPr>
       <t>测试集构造说明</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>读取并缓存共享光储备池输出的两个窗口状态；根据样本对索引获取目标状态 hi 和参考状态 hj；默认构造有符号状态差 hi-hj，并可对比状态差与状态拼接方式；使用 Ridge 回归读出层预测连续 CPI 差值 delta_cpi；通过 cpi_j + delta_cpi_hat 还原目标 CPI；对同一目标的多个参考预测结果进行平均或加权平均；统一计算 MAE、RMSE；整理普通光储备池与孪生光储备池回归模型的结果表及预测图</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>孪生回归读出与评估</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成共享光储备池状态比较、CPI 连续差值回归读出和统一评估代码框架</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态读取与校验脚本；孪生回归读出代码；统一评估脚本；模型参数与结果表；预测图及运行说明</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -962,7 +966,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="118.15">
@@ -977,7 +981,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="73.900000000000006">
@@ -991,10 +995,10 @@
         <v>14</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="75.75">
@@ -1006,10 +1010,10 @@
         <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="55.5">
@@ -1087,36 +1091,36 @@
     </row>
     <row r="3" spans="1:5" ht="83.25">
       <c r="A3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="4" spans="1:5" ht="55.5">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" ht="83.25">
+      <c r="A4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="C4" s="6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
